--- a/artfynd/A 23499-2025 artfynd.xlsx
+++ b/artfynd/A 23499-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY267"/>
+  <dimension ref="A1:AZ267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/240288</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
           <t>Floraväkteri Sverige</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/240289</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1012,6 +1027,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66397099</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1125,6 +1145,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66397210</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1238,6 +1263,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66397332</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1353,6 +1383,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62066434</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1459,6 +1494,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62066375</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1565,6 +1605,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62066376</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1671,6 +1716,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62066377</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1777,6 +1827,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62066378</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1883,6 +1938,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62066379</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1989,6 +2049,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62066380</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2095,6 +2160,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62066381</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2201,6 +2271,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62066382</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2307,6 +2382,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62066383</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2413,6 +2493,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62066384</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2519,6 +2604,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62066385</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2625,6 +2715,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62066386</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2731,6 +2826,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62066387</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2837,6 +2937,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62066388</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2943,6 +3048,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62066389</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3049,6 +3159,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62066390</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3155,6 +3270,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62066391</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3261,6 +3381,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62066392</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3367,6 +3492,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62066393</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3473,6 +3603,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62066439</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3597,6 +3732,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132594179</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3713,6 +3853,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2909659</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3815,6 +3960,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847733</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3917,6 +4067,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847734</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4019,6 +4174,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847735</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4121,6 +4281,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847736</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4223,6 +4388,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847737</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4325,6 +4495,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847738</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4427,6 +4602,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847739</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4529,6 +4709,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847740</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4631,6 +4816,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847741</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4733,6 +4923,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847742</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4835,6 +5030,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847743</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4937,6 +5137,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847744</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5039,6 +5244,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847745</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5141,6 +5351,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847746</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5243,6 +5458,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847747</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5345,6 +5565,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847748</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5447,6 +5672,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847749</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5549,6 +5779,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847750</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5651,6 +5886,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847751</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5753,6 +5993,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847752</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5855,6 +6100,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847753</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5957,6 +6207,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847754</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6059,6 +6314,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847755</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6161,6 +6421,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847756</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6263,6 +6528,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847757</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6365,6 +6635,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847758</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6467,6 +6742,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847759</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6569,6 +6849,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847760</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6671,6 +6956,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847761</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6773,6 +7063,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847762</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6884,6 +7179,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60847763</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6986,6 +7286,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309217</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7088,6 +7393,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309218</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7190,6 +7500,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309219</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7292,6 +7607,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309220</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7394,6 +7714,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309221</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7496,6 +7821,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309222</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7598,6 +7928,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309223</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7700,6 +8035,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309224</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7802,6 +8142,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309225</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7904,6 +8249,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309227</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8006,6 +8356,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309228</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8108,6 +8463,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309229</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8210,6 +8570,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309230</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8312,6 +8677,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309232</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8414,6 +8784,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309233</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8516,6 +8891,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309236</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8618,6 +8998,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309237</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8720,6 +9105,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309238</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8822,6 +9212,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309239</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8924,6 +9319,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309240</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9026,6 +9426,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309241</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9128,6 +9533,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309242</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9230,6 +9640,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309243</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9332,6 +9747,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309244</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9434,6 +9854,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309246</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9536,6 +9961,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309247</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9638,6 +10068,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309248</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9740,6 +10175,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309249</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9842,6 +10282,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309250</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9944,6 +10389,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309251</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10046,6 +10496,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309252</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10148,6 +10603,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309253</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10250,6 +10710,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309254</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10352,6 +10817,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309255</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10454,6 +10924,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309256</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10556,6 +11031,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309259</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10658,6 +11138,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61309260</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10774,6 +11259,11 @@
           <t>Naturvärdesinventering AFRY</t>
         </is>
       </c>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113060243</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -10899,6 +11389,11 @@
           <t>Naturvärdesinventering AFRY</t>
         </is>
       </c>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113060557</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11021,6 +11516,11 @@
       <c r="AY100" t="inlineStr">
         <is>
           <t>Naturvärdesinventering AFRY</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113060713</t>
         </is>
       </c>
     </row>
@@ -11141,6 +11641,11 @@
       <c r="AY101" t="inlineStr">
         <is>
           <t>Naturvärdesinventering AFRY</t>
+        </is>
+      </c>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113060762</t>
         </is>
       </c>
     </row>
@@ -11264,6 +11769,11 @@
           <t>Naturvärdesinventering AFRY</t>
         </is>
       </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113060843</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11386,6 +11896,11 @@
       <c r="AY103" t="inlineStr">
         <is>
           <t>Naturvärdesinventering AFRY</t>
+        </is>
+      </c>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113061079</t>
         </is>
       </c>
     </row>
@@ -11508,6 +12023,11 @@
           <t>Naturvärdesinventering AFRY</t>
         </is>
       </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113061157</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11626,6 +12146,11 @@
       <c r="AY105" t="inlineStr">
         <is>
           <t>Naturvärdesinventering AFRY</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113061250</t>
         </is>
       </c>
     </row>
@@ -11749,6 +12274,11 @@
           <t>Naturvärdesinventering AFRY</t>
         </is>
       </c>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113061459</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11851,6 +12381,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61299757</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11953,6 +12488,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61299758</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12055,6 +12595,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61299759</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12157,6 +12702,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61299760</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12259,6 +12809,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61299761</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12361,6 +12916,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61299762</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12463,6 +13023,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61299763</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12565,6 +13130,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61299764</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12667,6 +13237,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61380401</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12778,6 +13353,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4234640</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12880,6 +13460,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61315154</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -12982,6 +13567,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61315155</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13084,6 +13674,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61315156</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13186,6 +13781,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61315157</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13288,6 +13888,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61315158</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13390,6 +13995,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61315159</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13492,6 +14102,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61315160</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13594,6 +14209,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61315161</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13696,6 +14316,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61315162</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13798,6 +14423,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61315163</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -13900,6 +14530,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61315164</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14002,6 +14637,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61315165</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14104,6 +14744,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61315166</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14206,6 +14851,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61315167</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14308,6 +14958,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61315168</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14410,6 +15065,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61315169</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14512,6 +15172,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61315171</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14616,6 +15281,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66397249</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14733,6 +15403,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66397228</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14835,6 +15510,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61231654</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -14937,6 +15617,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61231655</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15039,6 +15724,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61231656</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15141,6 +15831,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61231657</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15243,6 +15938,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61231658</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15345,6 +16045,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61231659</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15447,6 +16152,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61231660</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15549,6 +16259,11 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61231661</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -15651,6 +16366,11 @@
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61231662</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
@@ -15753,6 +16473,11 @@
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61231664</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
@@ -15855,6 +16580,11 @@
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61231665</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
@@ -15957,6 +16687,11 @@
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61231666</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -16059,6 +16794,11 @@
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61231667</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -16161,6 +16901,11 @@
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
+      <c r="AZ149" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61231668</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
@@ -16263,6 +17008,11 @@
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
+      <c r="AZ150" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61231669</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
@@ -16365,6 +17115,11 @@
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
+      <c r="AZ151" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61231670</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
@@ -16467,6 +17222,11 @@
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
+      <c r="AZ152" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61231671</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
@@ -16569,6 +17329,11 @@
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
+      <c r="AZ153" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61231672</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -16671,6 +17436,11 @@
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
+      <c r="AZ154" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61231673</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -16773,6 +17543,11 @@
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
+      <c r="AZ155" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61231674</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
@@ -16875,6 +17650,11 @@
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
+      <c r="AZ156" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61231675</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -16977,6 +17757,11 @@
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
+      <c r="AZ157" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61231676</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -17081,6 +17866,11 @@
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
+      <c r="AZ158" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65205287</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
@@ -17197,6 +17987,11 @@
           <t>Naturvärdesinventering AFRY</t>
         </is>
       </c>
+      <c r="AZ159" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113061252</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
@@ -17299,6 +18094,11 @@
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
+      <c r="AZ160" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435177</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
@@ -17401,6 +18201,11 @@
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
+      <c r="AZ161" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435178</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
@@ -17503,6 +18308,11 @@
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
+      <c r="AZ162" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435180</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
@@ -17605,6 +18415,11 @@
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
+      <c r="AZ163" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435183</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
@@ -17707,6 +18522,11 @@
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
+      <c r="AZ164" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435184</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
@@ -17809,6 +18629,11 @@
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
+      <c r="AZ165" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435185</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
@@ -17911,6 +18736,11 @@
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
+      <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435186</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
@@ -18013,6 +18843,11 @@
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435187</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
@@ -18115,6 +18950,11 @@
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435188</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
@@ -18217,6 +19057,11 @@
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435189</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
@@ -18319,6 +19164,11 @@
         </is>
       </c>
       <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435190</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
@@ -18421,6 +19271,11 @@
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435191</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
@@ -18523,6 +19378,11 @@
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435192</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
@@ -18625,6 +19485,11 @@
         </is>
       </c>
       <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435193</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
@@ -18727,6 +19592,11 @@
         </is>
       </c>
       <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435195</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
@@ -18829,6 +19699,11 @@
         </is>
       </c>
       <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435196</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
@@ -18931,6 +19806,11 @@
         </is>
       </c>
       <c r="AY176" t="inlineStr"/>
+      <c r="AZ176" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435197</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
@@ -19033,6 +19913,11 @@
         </is>
       </c>
       <c r="AY177" t="inlineStr"/>
+      <c r="AZ177" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435198</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
@@ -19135,6 +20020,11 @@
         </is>
       </c>
       <c r="AY178" t="inlineStr"/>
+      <c r="AZ178" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435199</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
@@ -19237,6 +20127,11 @@
         </is>
       </c>
       <c r="AY179" t="inlineStr"/>
+      <c r="AZ179" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435200</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
@@ -19339,6 +20234,11 @@
         </is>
       </c>
       <c r="AY180" t="inlineStr"/>
+      <c r="AZ180" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435201</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
@@ -19441,6 +20341,11 @@
         </is>
       </c>
       <c r="AY181" t="inlineStr"/>
+      <c r="AZ181" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435203</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
@@ -19543,6 +20448,11 @@
         </is>
       </c>
       <c r="AY182" t="inlineStr"/>
+      <c r="AZ182" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435205</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
@@ -19645,6 +20555,11 @@
         </is>
       </c>
       <c r="AY183" t="inlineStr"/>
+      <c r="AZ183" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435206</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
@@ -19747,6 +20662,11 @@
         </is>
       </c>
       <c r="AY184" t="inlineStr"/>
+      <c r="AZ184" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435208</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
@@ -19849,6 +20769,11 @@
         </is>
       </c>
       <c r="AY185" t="inlineStr"/>
+      <c r="AZ185" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435209</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
@@ -19951,6 +20876,11 @@
         </is>
       </c>
       <c r="AY186" t="inlineStr"/>
+      <c r="AZ186" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435210</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
@@ -20053,6 +20983,11 @@
         </is>
       </c>
       <c r="AY187" t="inlineStr"/>
+      <c r="AZ187" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435211</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
@@ -20155,6 +21090,11 @@
         </is>
       </c>
       <c r="AY188" t="inlineStr"/>
+      <c r="AZ188" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435212</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
@@ -20257,6 +21197,11 @@
         </is>
       </c>
       <c r="AY189" t="inlineStr"/>
+      <c r="AZ189" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435214</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
@@ -20359,6 +21304,11 @@
         </is>
       </c>
       <c r="AY190" t="inlineStr"/>
+      <c r="AZ190" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435215</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
@@ -20461,6 +21411,11 @@
         </is>
       </c>
       <c r="AY191" t="inlineStr"/>
+      <c r="AZ191" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435217</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
@@ -20563,6 +21518,11 @@
         </is>
       </c>
       <c r="AY192" t="inlineStr"/>
+      <c r="AZ192" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435218</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
@@ -20665,6 +21625,11 @@
         </is>
       </c>
       <c r="AY193" t="inlineStr"/>
+      <c r="AZ193" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435219</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
@@ -20767,6 +21732,11 @@
         </is>
       </c>
       <c r="AY194" t="inlineStr"/>
+      <c r="AZ194" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435220</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
@@ -20869,6 +21839,11 @@
         </is>
       </c>
       <c r="AY195" t="inlineStr"/>
+      <c r="AZ195" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435221</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
@@ -20971,6 +21946,11 @@
         </is>
       </c>
       <c r="AY196" t="inlineStr"/>
+      <c r="AZ196" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435222</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
@@ -21073,6 +22053,11 @@
         </is>
       </c>
       <c r="AY197" t="inlineStr"/>
+      <c r="AZ197" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435223</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
@@ -21175,6 +22160,11 @@
         </is>
       </c>
       <c r="AY198" t="inlineStr"/>
+      <c r="AZ198" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435225</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
@@ -21277,6 +22267,11 @@
         </is>
       </c>
       <c r="AY199" t="inlineStr"/>
+      <c r="AZ199" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435226</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
@@ -21379,6 +22374,11 @@
         </is>
       </c>
       <c r="AY200" t="inlineStr"/>
+      <c r="AZ200" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435227</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
@@ -21481,6 +22481,11 @@
         </is>
       </c>
       <c r="AY201" t="inlineStr"/>
+      <c r="AZ201" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435228</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
@@ -21583,6 +22588,11 @@
         </is>
       </c>
       <c r="AY202" t="inlineStr"/>
+      <c r="AZ202" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435229</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
@@ -21685,6 +22695,11 @@
         </is>
       </c>
       <c r="AY203" t="inlineStr"/>
+      <c r="AZ203" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435230</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
@@ -21787,6 +22802,11 @@
         </is>
       </c>
       <c r="AY204" t="inlineStr"/>
+      <c r="AZ204" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435232</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
@@ -21889,6 +22909,11 @@
         </is>
       </c>
       <c r="AY205" t="inlineStr"/>
+      <c r="AZ205" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435233</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
@@ -21991,6 +23016,11 @@
         </is>
       </c>
       <c r="AY206" t="inlineStr"/>
+      <c r="AZ206" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435235</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
@@ -22093,6 +23123,11 @@
         </is>
       </c>
       <c r="AY207" t="inlineStr"/>
+      <c r="AZ207" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435236</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
@@ -22195,6 +23230,11 @@
         </is>
       </c>
       <c r="AY208" t="inlineStr"/>
+      <c r="AZ208" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435237</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
@@ -22297,6 +23337,11 @@
         </is>
       </c>
       <c r="AY209" t="inlineStr"/>
+      <c r="AZ209" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435239</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
@@ -22399,6 +23444,11 @@
         </is>
       </c>
       <c r="AY210" t="inlineStr"/>
+      <c r="AZ210" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435241</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
@@ -22501,6 +23551,11 @@
         </is>
       </c>
       <c r="AY211" t="inlineStr"/>
+      <c r="AZ211" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435243</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
@@ -22603,6 +23658,11 @@
         </is>
       </c>
       <c r="AY212" t="inlineStr"/>
+      <c r="AZ212" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58435328</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
@@ -22711,6 +23771,11 @@
         </is>
       </c>
       <c r="AY213" t="inlineStr"/>
+      <c r="AZ213" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/59074976</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
@@ -22815,6 +23880,11 @@
         </is>
       </c>
       <c r="AY214" t="inlineStr"/>
+      <c r="AZ214" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66397449</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
@@ -22931,6 +24001,11 @@
           <t>Naturvärdesinventering AFRY</t>
         </is>
       </c>
+      <c r="AZ215" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113060587</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
@@ -23047,6 +24122,11 @@
           <t>Naturvärdesinventering AFRY</t>
         </is>
       </c>
+      <c r="AZ216" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113061294</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
@@ -23149,6 +24229,11 @@
         </is>
       </c>
       <c r="AY217" t="inlineStr"/>
+      <c r="AZ217" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58814745</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
@@ -23251,6 +24336,11 @@
         </is>
       </c>
       <c r="AY218" t="inlineStr"/>
+      <c r="AZ218" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/58814746</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
@@ -23363,6 +24453,11 @@
         </is>
       </c>
       <c r="AY219" t="inlineStr"/>
+      <c r="AZ219" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66397437</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
@@ -23484,6 +24579,11 @@
           <t>Naturvärdesinventering AFRY</t>
         </is>
       </c>
+      <c r="AZ220" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113060236</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
@@ -23605,6 +24705,11 @@
           <t>Naturvärdesinventering AFRY</t>
         </is>
       </c>
+      <c r="AZ221" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113061314</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
@@ -23707,6 +24812,11 @@
         </is>
       </c>
       <c r="AY222" t="inlineStr"/>
+      <c r="AZ222" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298444</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
@@ -23809,6 +24919,11 @@
         </is>
       </c>
       <c r="AY223" t="inlineStr"/>
+      <c r="AZ223" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298445</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
@@ -23911,6 +25026,11 @@
         </is>
       </c>
       <c r="AY224" t="inlineStr"/>
+      <c r="AZ224" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298446</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
@@ -24013,6 +25133,11 @@
         </is>
       </c>
       <c r="AY225" t="inlineStr"/>
+      <c r="AZ225" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298447</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
@@ -24115,6 +25240,11 @@
         </is>
       </c>
       <c r="AY226" t="inlineStr"/>
+      <c r="AZ226" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298448</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
@@ -24217,6 +25347,11 @@
         </is>
       </c>
       <c r="AY227" t="inlineStr"/>
+      <c r="AZ227" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298449</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
@@ -24319,6 +25454,11 @@
         </is>
       </c>
       <c r="AY228" t="inlineStr"/>
+      <c r="AZ228" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298450</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
@@ -24421,6 +25561,11 @@
         </is>
       </c>
       <c r="AY229" t="inlineStr"/>
+      <c r="AZ229" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298451</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
@@ -24523,6 +25668,11 @@
         </is>
       </c>
       <c r="AY230" t="inlineStr"/>
+      <c r="AZ230" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298452</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
@@ -24625,6 +25775,11 @@
         </is>
       </c>
       <c r="AY231" t="inlineStr"/>
+      <c r="AZ231" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298453</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
@@ -24727,6 +25882,11 @@
         </is>
       </c>
       <c r="AY232" t="inlineStr"/>
+      <c r="AZ232" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298454</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
@@ -24829,6 +25989,11 @@
         </is>
       </c>
       <c r="AY233" t="inlineStr"/>
+      <c r="AZ233" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298456</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
@@ -24931,6 +26096,11 @@
         </is>
       </c>
       <c r="AY234" t="inlineStr"/>
+      <c r="AZ234" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298457</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
@@ -25033,6 +26203,11 @@
         </is>
       </c>
       <c r="AY235" t="inlineStr"/>
+      <c r="AZ235" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298458</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
@@ -25135,6 +26310,11 @@
         </is>
       </c>
       <c r="AY236" t="inlineStr"/>
+      <c r="AZ236" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298459</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
@@ -25237,6 +26417,11 @@
         </is>
       </c>
       <c r="AY237" t="inlineStr"/>
+      <c r="AZ237" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298460</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
@@ -25339,6 +26524,11 @@
         </is>
       </c>
       <c r="AY238" t="inlineStr"/>
+      <c r="AZ238" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298461</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
@@ -25441,6 +26631,11 @@
         </is>
       </c>
       <c r="AY239" t="inlineStr"/>
+      <c r="AZ239" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298462</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
@@ -25543,6 +26738,11 @@
         </is>
       </c>
       <c r="AY240" t="inlineStr"/>
+      <c r="AZ240" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298463</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
@@ -25645,6 +26845,11 @@
         </is>
       </c>
       <c r="AY241" t="inlineStr"/>
+      <c r="AZ241" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298464</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
@@ -25747,6 +26952,11 @@
         </is>
       </c>
       <c r="AY242" t="inlineStr"/>
+      <c r="AZ242" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298465</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
@@ -25849,6 +27059,11 @@
         </is>
       </c>
       <c r="AY243" t="inlineStr"/>
+      <c r="AZ243" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298466</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
@@ -25951,6 +27166,11 @@
         </is>
       </c>
       <c r="AY244" t="inlineStr"/>
+      <c r="AZ244" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298467</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
@@ -26053,6 +27273,11 @@
         </is>
       </c>
       <c r="AY245" t="inlineStr"/>
+      <c r="AZ245" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298468</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
@@ -26155,6 +27380,11 @@
         </is>
       </c>
       <c r="AY246" t="inlineStr"/>
+      <c r="AZ246" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298469</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
@@ -26257,6 +27487,11 @@
         </is>
       </c>
       <c r="AY247" t="inlineStr"/>
+      <c r="AZ247" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298470</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
@@ -26359,6 +27594,11 @@
         </is>
       </c>
       <c r="AY248" t="inlineStr"/>
+      <c r="AZ248" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298471</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
@@ -26461,6 +27701,11 @@
         </is>
       </c>
       <c r="AY249" t="inlineStr"/>
+      <c r="AZ249" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298472</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
@@ -26563,6 +27808,11 @@
         </is>
       </c>
       <c r="AY250" t="inlineStr"/>
+      <c r="AZ250" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298473</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
@@ -26665,6 +27915,11 @@
         </is>
       </c>
       <c r="AY251" t="inlineStr"/>
+      <c r="AZ251" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298474</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
@@ -26767,6 +28022,11 @@
         </is>
       </c>
       <c r="AY252" t="inlineStr"/>
+      <c r="AZ252" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298475</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
@@ -26869,6 +28129,11 @@
         </is>
       </c>
       <c r="AY253" t="inlineStr"/>
+      <c r="AZ253" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298476</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
@@ -26971,6 +28236,11 @@
         </is>
       </c>
       <c r="AY254" t="inlineStr"/>
+      <c r="AZ254" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298477</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
@@ -27073,6 +28343,11 @@
         </is>
       </c>
       <c r="AY255" t="inlineStr"/>
+      <c r="AZ255" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298478</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
@@ -27175,6 +28450,11 @@
         </is>
       </c>
       <c r="AY256" t="inlineStr"/>
+      <c r="AZ256" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298479</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
@@ -27277,6 +28557,11 @@
         </is>
       </c>
       <c r="AY257" t="inlineStr"/>
+      <c r="AZ257" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298480</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
@@ -27379,6 +28664,11 @@
         </is>
       </c>
       <c r="AY258" t="inlineStr"/>
+      <c r="AZ258" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298482</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
@@ -27481,6 +28771,11 @@
         </is>
       </c>
       <c r="AY259" t="inlineStr"/>
+      <c r="AZ259" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298483</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
@@ -27583,6 +28878,11 @@
         </is>
       </c>
       <c r="AY260" t="inlineStr"/>
+      <c r="AZ260" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298484</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
@@ -27685,6 +28985,11 @@
         </is>
       </c>
       <c r="AY261" t="inlineStr"/>
+      <c r="AZ261" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61298485</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
@@ -27789,6 +29094,11 @@
         </is>
       </c>
       <c r="AY262" t="inlineStr"/>
+      <c r="AZ262" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66397106</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
@@ -27893,6 +29203,11 @@
         </is>
       </c>
       <c r="AY263" t="inlineStr"/>
+      <c r="AZ263" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66397234</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
@@ -28014,6 +29329,11 @@
           <t>Naturvärdesinventering AFRY</t>
         </is>
       </c>
+      <c r="AZ264" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113060527</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
@@ -28130,6 +29450,11 @@
           <t>Naturvärdesinventering AFRY</t>
         </is>
       </c>
+      <c r="AZ265" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113060591</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
@@ -28251,6 +29576,11 @@
           <t>Naturvärdesinventering AFRY</t>
         </is>
       </c>
+      <c r="AZ266" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113061161</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
@@ -28372,8 +29702,281 @@
           <t>Naturvärdesinventering AFRY</t>
         </is>
       </c>
+      <c r="AZ267" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113061205</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ149" r:id="rId148"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ150" r:id="rId149"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ151" r:id="rId150"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ152" r:id="rId151"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ153" r:id="rId152"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ154" r:id="rId153"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ155" r:id="rId154"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ156" r:id="rId155"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ157" r:id="rId156"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ158" r:id="rId157"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ159" r:id="rId158"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ160" r:id="rId159"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ161" r:id="rId160"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ162" r:id="rId161"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ163" r:id="rId162"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ176" r:id="rId175"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ177" r:id="rId176"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ178" r:id="rId177"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ179" r:id="rId178"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ180" r:id="rId179"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ181" r:id="rId180"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ182" r:id="rId181"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ183" r:id="rId182"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ184" r:id="rId183"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ185" r:id="rId184"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ186" r:id="rId185"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ187" r:id="rId186"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ188" r:id="rId187"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ189" r:id="rId188"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ190" r:id="rId189"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ191" r:id="rId190"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ192" r:id="rId191"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ193" r:id="rId192"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ194" r:id="rId193"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ195" r:id="rId194"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ196" r:id="rId195"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ197" r:id="rId196"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ198" r:id="rId197"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ199" r:id="rId198"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ200" r:id="rId199"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ201" r:id="rId200"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ202" r:id="rId201"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ203" r:id="rId202"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ204" r:id="rId203"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ205" r:id="rId204"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ206" r:id="rId205"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ207" r:id="rId206"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ208" r:id="rId207"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ209" r:id="rId208"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ210" r:id="rId209"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ211" r:id="rId210"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ212" r:id="rId211"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ213" r:id="rId212"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ214" r:id="rId213"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ215" r:id="rId214"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ216" r:id="rId215"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ217" r:id="rId216"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ218" r:id="rId217"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ219" r:id="rId218"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ220" r:id="rId219"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ221" r:id="rId220"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ222" r:id="rId221"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ223" r:id="rId222"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ224" r:id="rId223"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ225" r:id="rId224"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ226" r:id="rId225"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ227" r:id="rId226"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ228" r:id="rId227"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ229" r:id="rId228"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ230" r:id="rId229"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ231" r:id="rId230"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ232" r:id="rId231"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ233" r:id="rId232"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ234" r:id="rId233"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ235" r:id="rId234"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ236" r:id="rId235"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ237" r:id="rId236"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ238" r:id="rId237"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ239" r:id="rId238"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ240" r:id="rId239"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ241" r:id="rId240"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ242" r:id="rId241"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ243" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ244" r:id="rId243"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ245" r:id="rId244"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ246" r:id="rId245"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ247" r:id="rId246"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ248" r:id="rId247"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ249" r:id="rId248"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ250" r:id="rId249"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ251" r:id="rId250"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ252" r:id="rId251"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ253" r:id="rId252"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ254" r:id="rId253"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ255" r:id="rId254"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ256" r:id="rId255"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ257" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ258" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ259" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ260" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ261" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ262" r:id="rId261"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ263" r:id="rId262"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ264" r:id="rId263"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ265" r:id="rId264"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ266" r:id="rId265"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ267" r:id="rId266"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>